--- a/words.xlsx
+++ b/words.xlsx
@@ -2088,7 +2088,7 @@
         <v>avión / aeroplano</v>
       </c>
       <c r="B100" t="str">
-        <v>airplane</v>
+        <v>airplane / aeroplane</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -3839,7 +3839,7 @@
         <v>catorce</v>
       </c>
       <c r="B203" t="str">
-        <v>14</v>
+        <v>14 / fourteen</v>
       </c>
       <c r="C203" t="str">
         <v/>
@@ -4162,7 +4162,7 @@
         <v>cien</v>
       </c>
       <c r="B222" t="str">
-        <v>hundred</v>
+        <v>100 / hundred</v>
       </c>
       <c r="C222" t="str">
         <v/>
@@ -4196,7 +4196,7 @@
         <v>cinco</v>
       </c>
       <c r="B224" t="str">
-        <v>five</v>
+        <v>5 / five</v>
       </c>
       <c r="C224" t="str">
         <v/>
@@ -4213,7 +4213,7 @@
         <v>cincuenta</v>
       </c>
       <c r="B225" t="str">
-        <v>50</v>
+        <v>50 / fifty</v>
       </c>
       <c r="C225" t="str">
         <v/>
@@ -4230,7 +4230,7 @@
         <v>cincuenta y cinco</v>
       </c>
       <c r="B226" t="str">
-        <v>55</v>
+        <v>55 fifty five</v>
       </c>
       <c r="C226" t="str">
         <v/>
@@ -4247,7 +4247,7 @@
         <v>cincuenta y cuatro</v>
       </c>
       <c r="B227" t="str">
-        <v>54</v>
+        <v>54 / fifty four</v>
       </c>
       <c r="C227" t="str">
         <v/>
@@ -4264,7 +4264,7 @@
         <v>cincuenta y dos</v>
       </c>
       <c r="B228" t="str">
-        <v>52</v>
+        <v>52 / fifty two</v>
       </c>
       <c r="C228" t="str">
         <v/>
@@ -4281,7 +4281,7 @@
         <v>cincuenta y nueve</v>
       </c>
       <c r="B229" t="str">
-        <v>59</v>
+        <v>59 / fifty nine</v>
       </c>
       <c r="C229" t="str">
         <v/>
@@ -4298,7 +4298,7 @@
         <v>cincuenta y ocho</v>
       </c>
       <c r="B230" t="str">
-        <v>58</v>
+        <v>58 / fifty eight</v>
       </c>
       <c r="C230" t="str">
         <v/>
@@ -4315,7 +4315,7 @@
         <v>cincuenta y seis</v>
       </c>
       <c r="B231" t="str">
-        <v>56</v>
+        <v>56 /fifty six</v>
       </c>
       <c r="C231" t="str">
         <v/>
@@ -4332,7 +4332,7 @@
         <v>cincuenta y siete</v>
       </c>
       <c r="B232" t="str">
-        <v>57</v>
+        <v>57 / fifty seven</v>
       </c>
       <c r="C232" t="str">
         <v/>
@@ -4349,7 +4349,7 @@
         <v>cincuenta y tres</v>
       </c>
       <c r="B233" t="str">
-        <v>53</v>
+        <v>53 / fifty three</v>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -4366,7 +4366,7 @@
         <v>cincuenta y uno</v>
       </c>
       <c r="B234" t="str">
-        <v>51</v>
+        <v>51 / fifty one</v>
       </c>
       <c r="C234" t="str">
         <v/>
@@ -5624,7 +5624,7 @@
         <v>cuarenta</v>
       </c>
       <c r="B308" t="str">
-        <v>40</v>
+        <v>40 / forty</v>
       </c>
       <c r="C308" t="str">
         <v/>
@@ -5641,7 +5641,7 @@
         <v>cuarenta y cinco</v>
       </c>
       <c r="B309" t="str">
-        <v>45</v>
+        <v>45 / forty five</v>
       </c>
       <c r="C309" t="str">
         <v/>
@@ -5658,7 +5658,7 @@
         <v>cuarenta y cuatro</v>
       </c>
       <c r="B310" t="str">
-        <v>44</v>
+        <v>44 / forty four</v>
       </c>
       <c r="C310" t="str">
         <v/>
@@ -5675,7 +5675,7 @@
         <v>cuarenta y dos</v>
       </c>
       <c r="B311" t="str">
-        <v>42</v>
+        <v>42 / forty two</v>
       </c>
       <c r="C311" t="str">
         <v/>
@@ -5692,7 +5692,7 @@
         <v>cuarenta y nueve</v>
       </c>
       <c r="B312" t="str">
-        <v>49</v>
+        <v>49 / forty nine</v>
       </c>
       <c r="C312" t="str">
         <v/>
@@ -5709,7 +5709,7 @@
         <v>cuarenta y ocho</v>
       </c>
       <c r="B313" t="str">
-        <v>48</v>
+        <v>48 / forty eight</v>
       </c>
       <c r="C313" t="str">
         <v/>
@@ -5726,7 +5726,7 @@
         <v>cuarenta y seis</v>
       </c>
       <c r="B314" t="str">
-        <v>46</v>
+        <v>46 / forty six</v>
       </c>
       <c r="C314" t="str">
         <v/>
@@ -5743,7 +5743,7 @@
         <v>cuarenta y siete</v>
       </c>
       <c r="B315" t="str">
-        <v>47</v>
+        <v>47 / forty seven</v>
       </c>
       <c r="C315" t="str">
         <v/>
@@ -5760,7 +5760,7 @@
         <v>cuarenta y tres</v>
       </c>
       <c r="B316" t="str">
-        <v>43</v>
+        <v>43 / forty three</v>
       </c>
       <c r="C316" t="str">
         <v/>
@@ -5777,7 +5777,7 @@
         <v>cuarenta y uno</v>
       </c>
       <c r="B317" t="str">
-        <v>41</v>
+        <v>41 / forty one</v>
       </c>
       <c r="C317" t="str">
         <v/>
@@ -5811,7 +5811,7 @@
         <v>cuatro</v>
       </c>
       <c r="B319" t="str">
-        <v>four</v>
+        <v>4 / four</v>
       </c>
       <c r="C319" t="str">
         <v/>
@@ -7001,7 +7001,7 @@
         <v>diecinueve</v>
       </c>
       <c r="B389" t="str">
-        <v>19</v>
+        <v>19 / nineteen</v>
       </c>
       <c r="C389" t="str">
         <v/>
@@ -7018,7 +7018,7 @@
         <v>dieciocho</v>
       </c>
       <c r="B390" t="str">
-        <v>18</v>
+        <v>18 / eighteen</v>
       </c>
       <c r="C390" t="str">
         <v/>
@@ -7035,7 +7035,7 @@
         <v>diecisiete</v>
       </c>
       <c r="B391" t="str">
-        <v>17</v>
+        <v>17 / seventeen</v>
       </c>
       <c r="C391" t="str">
         <v/>
@@ -7052,7 +7052,7 @@
         <v>dieciséis</v>
       </c>
       <c r="B392" t="str">
-        <v>16</v>
+        <v>16 / sixteen</v>
       </c>
       <c r="C392" t="str">
         <v/>
@@ -7086,7 +7086,7 @@
         <v>diez</v>
       </c>
       <c r="B394" t="str">
-        <v>ten</v>
+        <v>10 / ten</v>
       </c>
       <c r="C394" t="str">
         <v/>
@@ -7341,7 +7341,7 @@
         <v>doce</v>
       </c>
       <c r="B409" t="str">
-        <v>12</v>
+        <v>12 / twelve</v>
       </c>
       <c r="C409" t="str">
         <v/>
@@ -7528,7 +7528,7 @@
         <v>dos</v>
       </c>
       <c r="B420" t="str">
-        <v>two</v>
+        <v>2 / two</v>
       </c>
       <c r="C420" t="str">
         <v/>
@@ -13475,7 +13475,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>morado</v>
+        <v>morado / púrpura</v>
       </c>
       <c r="B770" t="str">
         <v>purple</v>
@@ -14532,7 +14532,7 @@
         <v>noventa</v>
       </c>
       <c r="B832" t="str">
-        <v>90</v>
+        <v>90 / ninety</v>
       </c>
       <c r="C832" t="str">
         <v/>
@@ -14549,7 +14549,7 @@
         <v>noventa y cinco</v>
       </c>
       <c r="B833" t="str">
-        <v>95</v>
+        <v>95 / ninety five</v>
       </c>
       <c r="C833" t="str">
         <v/>
@@ -14566,7 +14566,7 @@
         <v>noventa y cuatro</v>
       </c>
       <c r="B834" t="str">
-        <v>94</v>
+        <v>94 / ninety four</v>
       </c>
       <c r="C834" t="str">
         <v/>
@@ -14583,7 +14583,7 @@
         <v>noventa y dos</v>
       </c>
       <c r="B835" t="str">
-        <v>92</v>
+        <v>92 / ninety two</v>
       </c>
       <c r="C835" t="str">
         <v/>
@@ -14600,7 +14600,7 @@
         <v>noventa y nueve</v>
       </c>
       <c r="B836" t="str">
-        <v>99</v>
+        <v>99 / ninety nine</v>
       </c>
       <c r="C836" t="str">
         <v/>
@@ -14617,7 +14617,7 @@
         <v>noventa y ocho</v>
       </c>
       <c r="B837" t="str">
-        <v>98</v>
+        <v>98 / ninety eight</v>
       </c>
       <c r="C837" t="str">
         <v/>
@@ -14634,7 +14634,7 @@
         <v>noventa y seis</v>
       </c>
       <c r="B838" t="str">
-        <v>96</v>
+        <v>96 / ninety six</v>
       </c>
       <c r="C838" t="str">
         <v/>
@@ -14651,7 +14651,7 @@
         <v>noventa y siete</v>
       </c>
       <c r="B839" t="str">
-        <v>97</v>
+        <v>97 / ninety seven</v>
       </c>
       <c r="C839" t="str">
         <v/>
@@ -14668,7 +14668,7 @@
         <v>noventa y tres</v>
       </c>
       <c r="B840" t="str">
-        <v>93</v>
+        <v>93 / ninety three</v>
       </c>
       <c r="C840" t="str">
         <v/>
@@ -14685,7 +14685,7 @@
         <v>noventa y uno</v>
       </c>
       <c r="B841" t="str">
-        <v>91</v>
+        <v>91 / ninety one</v>
       </c>
       <c r="C841" t="str">
         <v/>
@@ -14804,7 +14804,7 @@
         <v>nueve</v>
       </c>
       <c r="B848" t="str">
-        <v>nine</v>
+        <v>9 / nine</v>
       </c>
       <c r="C848" t="str">
         <v/>
@@ -14957,7 +14957,7 @@
         <v>ochenta</v>
       </c>
       <c r="B857" t="str">
-        <v>80</v>
+        <v>80 / eighty</v>
       </c>
       <c r="C857" t="str">
         <v/>
@@ -14974,7 +14974,7 @@
         <v>ochenta y cinco</v>
       </c>
       <c r="B858" t="str">
-        <v>85</v>
+        <v>85 / eighty five</v>
       </c>
       <c r="C858" t="str">
         <v/>
@@ -14991,7 +14991,7 @@
         <v>ochenta y cuatro</v>
       </c>
       <c r="B859" t="str">
-        <v>84</v>
+        <v>84 / eighty four</v>
       </c>
       <c r="C859" t="str">
         <v/>
@@ -15008,7 +15008,7 @@
         <v>ochenta y dos</v>
       </c>
       <c r="B860" t="str">
-        <v>82</v>
+        <v>82 / eighty two</v>
       </c>
       <c r="C860" t="str">
         <v/>
@@ -15025,7 +15025,7 @@
         <v>ochenta y nueve</v>
       </c>
       <c r="B861" t="str">
-        <v>89</v>
+        <v>89 / eighty nine</v>
       </c>
       <c r="C861" t="str">
         <v/>
@@ -15042,7 +15042,7 @@
         <v>ochenta y ocho</v>
       </c>
       <c r="B862" t="str">
-        <v>88</v>
+        <v>88 / eighty eight</v>
       </c>
       <c r="C862" t="str">
         <v/>
@@ -15059,7 +15059,7 @@
         <v>ochenta y seis</v>
       </c>
       <c r="B863" t="str">
-        <v>86</v>
+        <v>86 / eighty six</v>
       </c>
       <c r="C863" t="str">
         <v/>
@@ -15076,7 +15076,7 @@
         <v>ochenta y siete</v>
       </c>
       <c r="B864" t="str">
-        <v>87</v>
+        <v>87 / eighty seven</v>
       </c>
       <c r="C864" t="str">
         <v/>
@@ -15093,7 +15093,7 @@
         <v>ochenta y tres</v>
       </c>
       <c r="B865" t="str">
-        <v>83</v>
+        <v>83 / eighty three</v>
       </c>
       <c r="C865" t="str">
         <v/>
@@ -15110,7 +15110,7 @@
         <v>ochenta y uno</v>
       </c>
       <c r="B866" t="str">
-        <v>81</v>
+        <v>81 / eighty one</v>
       </c>
       <c r="C866" t="str">
         <v/>
@@ -15127,7 +15127,7 @@
         <v>ocho</v>
       </c>
       <c r="B867" t="str">
-        <v>eight</v>
+        <v>8 / eight</v>
       </c>
       <c r="C867" t="str">
         <v/>
@@ -15348,7 +15348,7 @@
         <v>once</v>
       </c>
       <c r="B880" t="str">
-        <v>11</v>
+        <v>11 / eleven</v>
       </c>
       <c r="C880" t="str">
         <v/>
@@ -17827,7 +17827,7 @@
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>púrpura</v>
+        <v>púrpura / morado</v>
       </c>
       <c r="B1026" t="str">
         <v>purple</v>
@@ -17983,7 +17983,7 @@
         <v>quince</v>
       </c>
       <c r="B1035" t="str">
-        <v>15</v>
+        <v>15 / fifteen</v>
       </c>
       <c r="C1035" t="str">
         <v/>
@@ -19309,7 +19309,7 @@
         <v>seis</v>
       </c>
       <c r="B1113" t="str">
-        <v>six</v>
+        <v>six / six</v>
       </c>
       <c r="C1113" t="str">
         <v/>
@@ -19547,7 +19547,7 @@
         <v>sesenta</v>
       </c>
       <c r="B1127" t="str">
-        <v>60</v>
+        <v>60 / sixty</v>
       </c>
       <c r="C1127" t="str">
         <v/>
@@ -19564,7 +19564,7 @@
         <v>sesenta y cinco</v>
       </c>
       <c r="B1128" t="str">
-        <v>65</v>
+        <v>65 / sixty five</v>
       </c>
       <c r="C1128" t="str">
         <v/>
@@ -19581,7 +19581,7 @@
         <v>sesenta y cuatro</v>
       </c>
       <c r="B1129" t="str">
-        <v>64</v>
+        <v>64 / sixty four</v>
       </c>
       <c r="C1129" t="str">
         <v/>
@@ -19598,7 +19598,7 @@
         <v>sesenta y dos</v>
       </c>
       <c r="B1130" t="str">
-        <v>62</v>
+        <v>62 / sixty two</v>
       </c>
       <c r="C1130" t="str">
         <v/>
@@ -19615,7 +19615,7 @@
         <v>sesenta y nueve</v>
       </c>
       <c r="B1131" t="str">
-        <v>69</v>
+        <v>69 / sixty nine</v>
       </c>
       <c r="C1131" t="str">
         <v/>
@@ -19632,7 +19632,7 @@
         <v>sesenta y ocho</v>
       </c>
       <c r="B1132" t="str">
-        <v>68</v>
+        <v>68 / sixty eight</v>
       </c>
       <c r="C1132" t="str">
         <v/>
@@ -19649,7 +19649,7 @@
         <v>sesenta y seis</v>
       </c>
       <c r="B1133" t="str">
-        <v>66</v>
+        <v>66 / sixty six</v>
       </c>
       <c r="C1133" t="str">
         <v/>
@@ -19666,7 +19666,7 @@
         <v>sesenta y siete</v>
       </c>
       <c r="B1134" t="str">
-        <v>67</v>
+        <v>67 / sixty seven</v>
       </c>
       <c r="C1134" t="str">
         <v/>
@@ -19683,7 +19683,7 @@
         <v>sesenta y tres</v>
       </c>
       <c r="B1135" t="str">
-        <v>63</v>
+        <v>63 / sixty three</v>
       </c>
       <c r="C1135" t="str">
         <v/>
@@ -19700,7 +19700,7 @@
         <v>sesenta y uno</v>
       </c>
       <c r="B1136" t="str">
-        <v>61</v>
+        <v>61 / sixty one</v>
       </c>
       <c r="C1136" t="str">
         <v/>
@@ -19717,7 +19717,7 @@
         <v>setenta</v>
       </c>
       <c r="B1137" t="str">
-        <v>70</v>
+        <v>70 / seventy</v>
       </c>
       <c r="C1137" t="str">
         <v/>
@@ -19734,7 +19734,7 @@
         <v>setenta y cinco</v>
       </c>
       <c r="B1138" t="str">
-        <v>75</v>
+        <v>75 / seventy five</v>
       </c>
       <c r="C1138" t="str">
         <v/>
@@ -19751,7 +19751,7 @@
         <v>setenta y cuatro</v>
       </c>
       <c r="B1139" t="str">
-        <v>74</v>
+        <v>74 / seventy four</v>
       </c>
       <c r="C1139" t="str">
         <v/>
@@ -19768,7 +19768,7 @@
         <v>setenta y dos</v>
       </c>
       <c r="B1140" t="str">
-        <v>72</v>
+        <v>72 / seventy two</v>
       </c>
       <c r="C1140" t="str">
         <v/>
@@ -19785,7 +19785,7 @@
         <v>setenta y nueve</v>
       </c>
       <c r="B1141" t="str">
-        <v>79</v>
+        <v>79 / seventy nine</v>
       </c>
       <c r="C1141" t="str">
         <v/>
@@ -19802,7 +19802,7 @@
         <v>setenta y ocho</v>
       </c>
       <c r="B1142" t="str">
-        <v>78</v>
+        <v>78 / seventy eight</v>
       </c>
       <c r="C1142" t="str">
         <v/>
@@ -19819,7 +19819,7 @@
         <v>setenta y seis</v>
       </c>
       <c r="B1143" t="str">
-        <v>76</v>
+        <v>76 / seventy six</v>
       </c>
       <c r="C1143" t="str">
         <v/>
@@ -19836,7 +19836,7 @@
         <v>setenta y siete</v>
       </c>
       <c r="B1144" t="str">
-        <v>77</v>
+        <v>77 / seventy seven</v>
       </c>
       <c r="C1144" t="str">
         <v/>
@@ -19853,7 +19853,7 @@
         <v>setenta y tres</v>
       </c>
       <c r="B1145" t="str">
-        <v>73</v>
+        <v>73 / seventy three</v>
       </c>
       <c r="C1145" t="str">
         <v/>
@@ -19870,7 +19870,7 @@
         <v>setenta y uno</v>
       </c>
       <c r="B1146" t="str">
-        <v>71</v>
+        <v>71 / seventy one</v>
       </c>
       <c r="C1146" t="str">
         <v/>
@@ -20006,7 +20006,7 @@
         <v>siete</v>
       </c>
       <c r="B1154" t="str">
-        <v>seven</v>
+        <v>7 / seven</v>
       </c>
       <c r="C1154" t="str">
         <v/>
@@ -21740,7 +21740,7 @@
         <v>trece</v>
       </c>
       <c r="B1256" t="str">
-        <v>13</v>
+        <v>13 / thirteen</v>
       </c>
       <c r="C1256" t="str">
         <v/>
@@ -21757,7 +21757,7 @@
         <v>treinta</v>
       </c>
       <c r="B1257" t="str">
-        <v>30</v>
+        <v>30 / thirty</v>
       </c>
       <c r="C1257" t="str">
         <v/>
@@ -21774,7 +21774,7 @@
         <v>treinta y cinco</v>
       </c>
       <c r="B1258" t="str">
-        <v>35</v>
+        <v>35 / thirty five</v>
       </c>
       <c r="C1258" t="str">
         <v/>
@@ -21791,7 +21791,7 @@
         <v>treinta y cuatro</v>
       </c>
       <c r="B1259" t="str">
-        <v>34</v>
+        <v>34 / thirty four</v>
       </c>
       <c r="C1259" t="str">
         <v/>
@@ -21808,7 +21808,7 @@
         <v>treinta y dos</v>
       </c>
       <c r="B1260" t="str">
-        <v>32</v>
+        <v>32 / thirty two</v>
       </c>
       <c r="C1260" t="str">
         <v/>
@@ -21825,7 +21825,7 @@
         <v>treinta y nueve</v>
       </c>
       <c r="B1261" t="str">
-        <v>39</v>
+        <v>39 / thirty nine</v>
       </c>
       <c r="C1261" t="str">
         <v/>
@@ -21842,7 +21842,7 @@
         <v>treinta y ocho</v>
       </c>
       <c r="B1262" t="str">
-        <v>38</v>
+        <v>38 / thirty eight</v>
       </c>
       <c r="C1262" t="str">
         <v/>
@@ -21859,7 +21859,7 @@
         <v>treinta y seis</v>
       </c>
       <c r="B1263" t="str">
-        <v>36</v>
+        <v>36 / thirty six</v>
       </c>
       <c r="C1263" t="str">
         <v/>
@@ -21876,7 +21876,7 @@
         <v>treinta y siete</v>
       </c>
       <c r="B1264" t="str">
-        <v>37</v>
+        <v>37 / thirty seven</v>
       </c>
       <c r="C1264" t="str">
         <v/>
@@ -21893,7 +21893,7 @@
         <v>treinta y tres</v>
       </c>
       <c r="B1265" t="str">
-        <v>33</v>
+        <v>33 / thirty three</v>
       </c>
       <c r="C1265" t="str">
         <v/>
@@ -21910,7 +21910,7 @@
         <v>treinta y uno</v>
       </c>
       <c r="B1266" t="str">
-        <v>31</v>
+        <v>31 / thirty one</v>
       </c>
       <c r="C1266" t="str">
         <v/>
@@ -21944,7 +21944,7 @@
         <v>tres</v>
       </c>
       <c r="B1268" t="str">
-        <v>three</v>
+        <v>3 / three</v>
       </c>
       <c r="C1268" t="str">
         <v/>
@@ -22199,7 +22199,7 @@
         <v>uno</v>
       </c>
       <c r="B1283" t="str">
-        <v>one</v>
+        <v>1 / one</v>
       </c>
       <c r="C1283" t="str">
         <v/>
@@ -22369,7 +22369,7 @@
         <v>veinte</v>
       </c>
       <c r="B1293" t="str">
-        <v>twenty</v>
+        <v>20 / twenty</v>
       </c>
       <c r="C1293" t="str">
         <v/>
@@ -22386,7 +22386,7 @@
         <v>veinticinco</v>
       </c>
       <c r="B1294" t="str">
-        <v>25</v>
+        <v>25 / twenty five</v>
       </c>
       <c r="C1294" t="str">
         <v/>
@@ -22403,7 +22403,7 @@
         <v>veinticuatro</v>
       </c>
       <c r="B1295" t="str">
-        <v>24</v>
+        <v>24 / twenty four</v>
       </c>
       <c r="C1295" t="str">
         <v/>
@@ -22420,7 +22420,7 @@
         <v>veintidós</v>
       </c>
       <c r="B1296" t="str">
-        <v>22</v>
+        <v>22 / twenty two</v>
       </c>
       <c r="C1296" t="str">
         <v/>
@@ -22437,7 +22437,7 @@
         <v>veintinueve</v>
       </c>
       <c r="B1297" t="str">
-        <v>29</v>
+        <v>29 / twenty nine</v>
       </c>
       <c r="C1297" t="str">
         <v/>
@@ -22454,7 +22454,7 @@
         <v>veintiocho</v>
       </c>
       <c r="B1298" t="str">
-        <v>28</v>
+        <v>28 / twenty eight</v>
       </c>
       <c r="C1298" t="str">
         <v/>
@@ -22471,7 +22471,7 @@
         <v>veintisiete</v>
       </c>
       <c r="B1299" t="str">
-        <v>27</v>
+        <v>27 / twenty seven</v>
       </c>
       <c r="C1299" t="str">
         <v/>
@@ -22488,7 +22488,7 @@
         <v>veintiséis</v>
       </c>
       <c r="B1300" t="str">
-        <v>26</v>
+        <v>26 / twenty six</v>
       </c>
       <c r="C1300" t="str">
         <v/>
@@ -22505,7 +22505,7 @@
         <v>veintitrés</v>
       </c>
       <c r="B1301" t="str">
-        <v>23</v>
+        <v>23 / twenty three</v>
       </c>
       <c r="C1301" t="str">
         <v/>
@@ -22522,7 +22522,7 @@
         <v>veintiuno</v>
       </c>
       <c r="B1302" t="str">
-        <v>21</v>
+        <v>21 / twenty one</v>
       </c>
       <c r="C1302" t="str">
         <v/>

--- a/words.xlsx
+++ b/words.xlsx
@@ -861,7 +861,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>adiós</v>
+        <v>adiós / chao</v>
       </c>
       <c r="B28" t="str">
         <v>goodbye</v>
@@ -3975,7 +3975,7 @@
         <v>centro</v>
       </c>
       <c r="B211" t="str">
-        <v>center</v>
+        <v>centre / center</v>
       </c>
       <c r="C211" t="str">
         <v/>
@@ -4009,7 +4009,7 @@
         <v>cerdo</v>
       </c>
       <c r="B213" t="str">
-        <v>pig</v>
+        <v>pig / pork</v>
       </c>
       <c r="C213" t="str">
         <v/>
@@ -4060,7 +4060,7 @@
         <v>cerveza</v>
       </c>
       <c r="B216" t="str">
-        <v>beer</v>
+        <v>beer / lager</v>
       </c>
       <c r="C216" t="str">
         <v/>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>chao</v>
+        <v>chao / adiós</v>
       </c>
       <c r="B217" t="str">
         <v>bye</v>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>chica</v>
+        <v>chica / niña / nena</v>
       </c>
       <c r="B219" t="str">
         <v>girl</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>chico</v>
+        <v>chico / muchacho / niño</v>
       </c>
       <c r="B220" t="str">
         <v>boy</v>
@@ -4434,7 +4434,7 @@
         <v>cita</v>
       </c>
       <c r="B238" t="str">
-        <v>appointment</v>
+        <v>appointment / date</v>
       </c>
       <c r="C238" t="str">
         <v/>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>coche</v>
+        <v>coche / carro / auto</v>
       </c>
       <c r="B245" t="str">
         <v>car</v>
@@ -4652,10 +4652,10 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>colegio</v>
+        <v>colegio / escuela</v>
       </c>
       <c r="B251" t="str">
-        <v>school</v>
+        <v>school / college</v>
       </c>
       <c r="C251" t="str">
         <v/>
@@ -4672,7 +4672,7 @@
         <v>color</v>
       </c>
       <c r="B252" t="str">
-        <v>color</v>
+        <v>colour / color</v>
       </c>
       <c r="C252" t="str">
         <v/>
@@ -5049,7 +5049,7 @@
         <v>to know</v>
       </c>
       <c r="C274" t="str">
-        <v>people/places</v>
+        <v>people or places</v>
       </c>
       <c r="D274" t="str">
         <v>conjugation</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>copa</v>
+        <v>copa / vaso</v>
       </c>
       <c r="B289" t="str">
         <v>glass</v>
@@ -5369,10 +5369,10 @@
         <v>correcto</v>
       </c>
       <c r="B293" t="str">
-        <v>right</v>
+        <v>right / correct</v>
       </c>
       <c r="C293" t="str">
-        <v/>
+        <v>not the direction</v>
       </c>
       <c r="D293" t="str">
         <v/>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>cuarto</v>
+        <v>cuarto / habitación</v>
       </c>
       <c r="B318" t="str">
         <v>room</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>cuestión</v>
+        <v>cuestión / pregunta</v>
       </c>
       <c r="B324" t="str">
         <v>question</v>
@@ -5947,7 +5947,7 @@
         <v>culpa</v>
       </c>
       <c r="B327" t="str">
-        <v>fault</v>
+        <v>blame / fault</v>
       </c>
       <c r="C327" t="str">
         <v/>
@@ -6134,7 +6134,7 @@
         <v>cárcel</v>
       </c>
       <c r="B338" t="str">
-        <v>jail</v>
+        <v>jail / prison</v>
       </c>
       <c r="C338" t="str">
         <v/>
@@ -6205,7 +6205,7 @@
         <v>how are you?</v>
       </c>
       <c r="C342" t="str">
-        <v/>
+        <v>informal</v>
       </c>
       <c r="D342" t="str">
         <v>greetings</v>
@@ -6613,7 +6613,7 @@
         <v>right</v>
       </c>
       <c r="C366" t="str">
-        <v/>
+        <v>direction</v>
       </c>
       <c r="D366" t="str">
         <v/>
@@ -6630,7 +6630,7 @@
         <v>right</v>
       </c>
       <c r="C367" t="str">
-        <v/>
+        <v>direction</v>
       </c>
       <c r="D367" t="str">
         <v/>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>despacio</v>
+        <v>despacio / lentamente</v>
       </c>
       <c r="B376" t="str">
         <v>slowly</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>despertar</v>
+        <v>despertar / despertarse</v>
       </c>
       <c r="B378" t="str">
         <v>to wake up</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>despertarse</v>
+        <v>despertarse / despertarse</v>
       </c>
       <c r="B379" t="str">
         <v>to wake up</v>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>muchacho</v>
+        <v>muchacho / niño / chico</v>
       </c>
       <c r="B778" t="str">
         <v>boy</v>
@@ -14121,7 +14121,7 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>nena</v>
+        <v>nena / niña / chica</v>
       </c>
       <c r="B808" t="str">
         <v>girl</v>
@@ -14308,7 +14308,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>niña</v>
+        <v>niña / nena / chica</v>
       </c>
       <c r="B819" t="str">
         <v>girl</v>
@@ -14325,10 +14325,10 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>niño</v>
+        <v>niño / muchacho / chico</v>
       </c>
       <c r="B820" t="str">
-        <v>kid</v>
+        <v>kid / boy</v>
       </c>
       <c r="C820" t="str">
         <v/>
